--- a/Sensitivity_PSNR_Pirate.xlsx
+++ b/Sensitivity_PSNR_Pirate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEF2F6BC-C9D8-4484-BBAC-BA64B6537DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BC5DE7E-0483-4CCB-A006-F2475F7BD813}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D2600FC-A084-4894-B0F7-B6C9AA0DA72F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8E3F579D-6CD9-4C72-92C5-9261C89B00FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF63B51-E495-4A64-BD23-719CE80F276F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6AAE7C6-338F-4EE3-9E51-E0BFC4E75B34}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF999407-4B6D-4E76-BDD8-AEC7A4B29E1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A8A7373-7C37-4209-B749-4C49E63127B9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42F8B448-3259-42D1-B4E5-E8560759D155}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AEDD2AC-436B-4905-8C63-67E85D2FD5CF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
